--- a/【エネマネ】【UT_試験項目表】EMS-SW-02_電力量確認画面スマホ/【エネマネ】【UT_試験項目表】EMS-SW02_電力量確認画面スマホ版_Jp Ver.xlsx
+++ b/【エネマネ】【UT_試験項目表】EMS-SW-02_電力量確認画面スマホ/【エネマネ】【UT_試験項目表】EMS-SW02_電力量確認画面スマホ版_Jp Ver.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10212"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6613721F-E439-0A44-BD0D-02D65E4C2595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F37A56-BD53-6D4F-BF80-25A36760344B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="700" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="タイトル" sheetId="5" r:id="rId1"/>
@@ -1321,6 +1321,294 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="4" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="3" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1330,41 +1618,26 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1375,149 +1648,35 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="3" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="4" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1557,165 +1716,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -2148,124 +2148,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="65" t="s">
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65" t="s">
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="65" t="s">
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65" t="s">
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="65"/>
+      <c r="T1" s="77"/>
       <c r="U1" s="11"/>
       <c r="V1" s="11"/>
     </row>
     <row r="2" spans="1:47">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="56" t="s">
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="112" t="s">
         <v>74</v>
       </c>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="57" t="s">
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="56"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="112"/>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
     </row>
     <row r="3" spans="1:47">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="77" t="s">
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65" t="s">
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65" t="s">
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="65"/>
+      <c r="T3" s="77"/>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
     </row>
     <row r="4" spans="1:47" ht="28" customHeight="1">
-      <c r="A4" s="91"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="83" t="s">
+      <c r="A4" s="106"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="87"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="70"/>
-      <c r="T4" s="71"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="101"/>
       <c r="U4" s="11"/>
       <c r="V4" s="11"/>
     </row>
@@ -2297,91 +2297,91 @@
       <c r="A6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="119" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="74" t="s">
+      <c r="C6" s="120"/>
+      <c r="D6" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="67" t="s">
+      <c r="E6" s="122"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="69"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="94"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
+      <c r="T6" s="95"/>
       <c r="U6" s="17"/>
       <c r="V6" s="17"/>
     </row>
     <row r="7" spans="1:47" ht="28.5" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="67" t="s">
+      <c r="B7" s="72"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="49" t="s">
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="66"/>
-      <c r="T7" s="66"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="127"/>
+      <c r="Q7" s="117"/>
+      <c r="R7" s="117"/>
+      <c r="S7" s="117"/>
+      <c r="T7" s="117"/>
       <c r="U7" s="18"/>
       <c r="V7" s="18"/>
     </row>
     <row r="8" spans="1:47" ht="13.5" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="67" t="s">
+      <c r="B8" s="72"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="93" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="49" t="s">
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="66"/>
-      <c r="T8" s="66"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117"/>
+      <c r="S8" s="117"/>
+      <c r="T8" s="117"/>
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
     </row>
@@ -2389,1081 +2389,1223 @@
       <c r="A10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="48"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="111"/>
       <c r="F10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="93" t="s">
+      <c r="G10" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="88" t="s">
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="83"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="N10" s="88"/>
-      <c r="O10" s="88"/>
-      <c r="P10" s="88"/>
-      <c r="Q10" s="88"/>
-      <c r="R10" s="59" t="s">
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="S10" s="60"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="60"/>
-      <c r="V10" s="61"/>
-      <c r="W10" s="59" t="s">
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="73"/>
+      <c r="W10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-      <c r="Z10" s="60"/>
-      <c r="AA10" s="60"/>
-      <c r="AB10" s="61"/>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="72"/>
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="72"/>
+      <c r="AB10" s="73"/>
       <c r="AC10" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="AD10" s="46" t="s">
+      <c r="AD10" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="AE10" s="47"/>
-      <c r="AF10" s="48"/>
-      <c r="AG10" s="46" t="s">
+      <c r="AE10" s="110"/>
+      <c r="AF10" s="111"/>
+      <c r="AG10" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="AH10" s="47"/>
-      <c r="AI10" s="48"/>
-      <c r="AJ10" s="59" t="s">
+      <c r="AH10" s="110"/>
+      <c r="AI10" s="111"/>
+      <c r="AJ10" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="AK10" s="61"/>
-      <c r="AL10" s="59" t="s">
+      <c r="AK10" s="73"/>
+      <c r="AL10" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="AM10" s="61"/>
-      <c r="AN10" s="59" t="s">
+      <c r="AM10" s="73"/>
+      <c r="AN10" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="AO10" s="61"/>
-      <c r="AP10" s="59" t="s">
+      <c r="AO10" s="73"/>
+      <c r="AP10" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="AQ10" s="61"/>
-      <c r="AR10" s="88" t="s">
+      <c r="AQ10" s="73"/>
+      <c r="AR10" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="AS10" s="88"/>
-      <c r="AT10" s="88"/>
-      <c r="AU10" s="88"/>
+      <c r="AS10" s="69"/>
+      <c r="AT10" s="69"/>
+      <c r="AU10" s="69"/>
     </row>
     <row r="11" spans="1:47" ht="150.5" customHeight="1">
       <c r="A11" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="52"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="130"/>
       <c r="F11" s="21">
         <v>1</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34" t="s">
+      <c r="H11" s="78"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="31" t="s">
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="34" t="s">
+      <c r="S11" s="56"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="56"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="X11" s="34"/>
-      <c r="Y11" s="34"/>
-      <c r="Z11" s="34"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="34"/>
+      <c r="X11" s="78"/>
+      <c r="Y11" s="78"/>
+      <c r="Z11" s="78"/>
+      <c r="AA11" s="78"/>
+      <c r="AB11" s="78"/>
       <c r="AC11" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="AD11" s="40"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="40"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="40"/>
-      <c r="AJ11" s="40"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="40"/>
-      <c r="AM11" s="40"/>
-      <c r="AN11" s="40"/>
-      <c r="AO11" s="40"/>
-      <c r="AP11" s="40"/>
-      <c r="AQ11" s="40"/>
-      <c r="AR11" s="40"/>
-      <c r="AS11" s="40"/>
-      <c r="AT11" s="40"/>
-      <c r="AU11" s="40"/>
+      <c r="AD11" s="70"/>
+      <c r="AE11" s="70"/>
+      <c r="AF11" s="70"/>
+      <c r="AG11" s="70"/>
+      <c r="AH11" s="70"/>
+      <c r="AI11" s="70"/>
+      <c r="AJ11" s="70"/>
+      <c r="AK11" s="70"/>
+      <c r="AL11" s="70"/>
+      <c r="AM11" s="70"/>
+      <c r="AN11" s="70"/>
+      <c r="AO11" s="70"/>
+      <c r="AP11" s="70"/>
+      <c r="AQ11" s="70"/>
+      <c r="AR11" s="70"/>
+      <c r="AS11" s="70"/>
+      <c r="AT11" s="70"/>
+      <c r="AU11" s="70"/>
     </row>
     <row r="12" spans="1:47" ht="73.5" customHeight="1">
       <c r="A12" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="126"/>
       <c r="F12" s="21">
         <v>2</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34" t="s">
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="31" t="s">
+      <c r="N12" s="78"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="78"/>
+      <c r="Q12" s="78"/>
+      <c r="R12" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="36"/>
-      <c r="W12" s="34" t="s">
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="56"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="X12" s="34"/>
-      <c r="Y12" s="34"/>
-      <c r="Z12" s="34"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="34"/>
+      <c r="X12" s="78"/>
+      <c r="Y12" s="78"/>
+      <c r="Z12" s="78"/>
+      <c r="AA12" s="78"/>
+      <c r="AB12" s="78"/>
       <c r="AC12" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="AD12" s="40"/>
-      <c r="AE12" s="40"/>
-      <c r="AF12" s="40"/>
-      <c r="AG12" s="40"/>
-      <c r="AH12" s="40"/>
-      <c r="AI12" s="40"/>
-      <c r="AJ12" s="40"/>
-      <c r="AK12" s="40"/>
-      <c r="AL12" s="40"/>
-      <c r="AM12" s="40"/>
-      <c r="AN12" s="40"/>
-      <c r="AO12" s="40"/>
-      <c r="AP12" s="40"/>
-      <c r="AQ12" s="40"/>
-      <c r="AR12" s="40"/>
-      <c r="AS12" s="40"/>
-      <c r="AT12" s="40"/>
-      <c r="AU12" s="40"/>
+      <c r="AD12" s="70"/>
+      <c r="AE12" s="70"/>
+      <c r="AF12" s="70"/>
+      <c r="AG12" s="70"/>
+      <c r="AH12" s="70"/>
+      <c r="AI12" s="70"/>
+      <c r="AJ12" s="70"/>
+      <c r="AK12" s="70"/>
+      <c r="AL12" s="70"/>
+      <c r="AM12" s="70"/>
+      <c r="AN12" s="70"/>
+      <c r="AO12" s="70"/>
+      <c r="AP12" s="70"/>
+      <c r="AQ12" s="70"/>
+      <c r="AR12" s="70"/>
+      <c r="AS12" s="70"/>
+      <c r="AT12" s="70"/>
+      <c r="AU12" s="70"/>
     </row>
     <row r="13" spans="1:47" ht="93" customHeight="1">
       <c r="A13" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="126"/>
       <c r="F13" s="21">
         <v>3</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34" t="s">
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="31" t="s">
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="78"/>
+      <c r="Q13" s="78"/>
+      <c r="R13" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="36"/>
-      <c r="W13" s="34" t="s">
+      <c r="S13" s="56"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="56"/>
+      <c r="V13" s="57"/>
+      <c r="W13" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
+      <c r="X13" s="78"/>
+      <c r="Y13" s="78"/>
+      <c r="Z13" s="78"/>
+      <c r="AA13" s="78"/>
+      <c r="AB13" s="78"/>
       <c r="AC13" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="AD13" s="40"/>
-      <c r="AE13" s="40"/>
-      <c r="AF13" s="40"/>
-      <c r="AG13" s="40"/>
-      <c r="AH13" s="40"/>
-      <c r="AI13" s="40"/>
-      <c r="AJ13" s="40"/>
-      <c r="AK13" s="40"/>
-      <c r="AL13" s="40"/>
-      <c r="AM13" s="40"/>
-      <c r="AN13" s="40"/>
-      <c r="AO13" s="40"/>
-      <c r="AP13" s="40"/>
-      <c r="AQ13" s="40"/>
-      <c r="AR13" s="40"/>
-      <c r="AS13" s="40"/>
-      <c r="AT13" s="40"/>
-      <c r="AU13" s="40"/>
+      <c r="AD13" s="70"/>
+      <c r="AE13" s="70"/>
+      <c r="AF13" s="70"/>
+      <c r="AG13" s="70"/>
+      <c r="AH13" s="70"/>
+      <c r="AI13" s="70"/>
+      <c r="AJ13" s="70"/>
+      <c r="AK13" s="70"/>
+      <c r="AL13" s="70"/>
+      <c r="AM13" s="70"/>
+      <c r="AN13" s="70"/>
+      <c r="AO13" s="70"/>
+      <c r="AP13" s="70"/>
+      <c r="AQ13" s="70"/>
+      <c r="AR13" s="70"/>
+      <c r="AS13" s="70"/>
+      <c r="AT13" s="70"/>
+      <c r="AU13" s="70"/>
     </row>
     <row r="14" spans="1:47" ht="70" customHeight="1">
       <c r="A14" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="55"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="133"/>
       <c r="F14" s="21">
         <v>4</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="78" t="s">
         <v>123</v>
       </c>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34" t="s">
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="31" t="s">
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="36"/>
-      <c r="W14" s="34" t="s">
+      <c r="S14" s="56"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="56"/>
+      <c r="V14" s="57"/>
+      <c r="W14" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="41"/>
-      <c r="Z14" s="41"/>
-      <c r="AA14" s="41"/>
-      <c r="AB14" s="41"/>
+      <c r="X14" s="79"/>
+      <c r="Y14" s="79"/>
+      <c r="Z14" s="79"/>
+      <c r="AA14" s="79"/>
+      <c r="AB14" s="79"/>
       <c r="AC14" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="AD14" s="40"/>
-      <c r="AE14" s="40"/>
-      <c r="AF14" s="40"/>
-      <c r="AG14" s="40"/>
-      <c r="AH14" s="40"/>
-      <c r="AI14" s="40"/>
-      <c r="AJ14" s="40"/>
-      <c r="AK14" s="40"/>
-      <c r="AL14" s="40"/>
-      <c r="AM14" s="40"/>
-      <c r="AN14" s="40"/>
-      <c r="AO14" s="40"/>
-      <c r="AP14" s="40"/>
-      <c r="AQ14" s="40"/>
-      <c r="AR14" s="40"/>
-      <c r="AS14" s="40"/>
-      <c r="AT14" s="40"/>
-      <c r="AU14" s="40"/>
-    </row>
-    <row r="15" spans="1:47" s="133" customFormat="1" ht="71" customHeight="1">
-      <c r="A15" s="118" t="s">
+      <c r="AD14" s="70"/>
+      <c r="AE14" s="70"/>
+      <c r="AF14" s="70"/>
+      <c r="AG14" s="70"/>
+      <c r="AH14" s="70"/>
+      <c r="AI14" s="70"/>
+      <c r="AJ14" s="70"/>
+      <c r="AK14" s="70"/>
+      <c r="AL14" s="70"/>
+      <c r="AM14" s="70"/>
+      <c r="AN14" s="70"/>
+      <c r="AO14" s="70"/>
+      <c r="AP14" s="70"/>
+      <c r="AQ14" s="70"/>
+      <c r="AR14" s="70"/>
+      <c r="AS14" s="70"/>
+      <c r="AT14" s="70"/>
+      <c r="AU14" s="70"/>
+    </row>
+    <row r="15" spans="1:47" s="35" customFormat="1" ht="71" customHeight="1">
+      <c r="A15" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="119" t="s">
+      <c r="B15" s="138" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122">
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="33">
         <v>5</v>
       </c>
-      <c r="G15" s="123" t="s">
+      <c r="G15" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="124"/>
-      <c r="I15" s="124"/>
-      <c r="J15" s="124"/>
-      <c r="K15" s="124"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="126" t="s">
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="143"/>
+      <c r="M15" s="144" t="s">
         <v>80</v>
       </c>
-      <c r="N15" s="126"/>
-      <c r="O15" s="126"/>
-      <c r="P15" s="126"/>
-      <c r="Q15" s="126"/>
-      <c r="R15" s="123" t="s">
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="141" t="s">
         <v>137</v>
       </c>
-      <c r="S15" s="127"/>
-      <c r="T15" s="127"/>
-      <c r="U15" s="127"/>
-      <c r="V15" s="128"/>
-      <c r="W15" s="123" t="s">
+      <c r="S15" s="145"/>
+      <c r="T15" s="145"/>
+      <c r="U15" s="145"/>
+      <c r="V15" s="146"/>
+      <c r="W15" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="X15" s="124"/>
-      <c r="Y15" s="124"/>
-      <c r="Z15" s="124"/>
-      <c r="AA15" s="124"/>
-      <c r="AB15" s="125"/>
-      <c r="AC15" s="129"/>
-      <c r="AD15" s="130"/>
-      <c r="AE15" s="131"/>
-      <c r="AF15" s="132"/>
-      <c r="AG15" s="130"/>
-      <c r="AH15" s="131"/>
-      <c r="AI15" s="132"/>
-      <c r="AJ15" s="130"/>
-      <c r="AK15" s="132"/>
-      <c r="AL15" s="130"/>
-      <c r="AM15" s="132"/>
-      <c r="AN15" s="130"/>
-      <c r="AO15" s="132"/>
-      <c r="AP15" s="130"/>
-      <c r="AQ15" s="132"/>
-      <c r="AR15" s="130"/>
-      <c r="AS15" s="131"/>
-      <c r="AT15" s="131"/>
-      <c r="AU15" s="132"/>
+      <c r="X15" s="142"/>
+      <c r="Y15" s="142"/>
+      <c r="Z15" s="142"/>
+      <c r="AA15" s="142"/>
+      <c r="AB15" s="143"/>
+      <c r="AC15" s="34"/>
+      <c r="AD15" s="74"/>
+      <c r="AE15" s="76"/>
+      <c r="AF15" s="75"/>
+      <c r="AG15" s="74"/>
+      <c r="AH15" s="76"/>
+      <c r="AI15" s="75"/>
+      <c r="AJ15" s="74"/>
+      <c r="AK15" s="75"/>
+      <c r="AL15" s="74"/>
+      <c r="AM15" s="75"/>
+      <c r="AN15" s="74"/>
+      <c r="AO15" s="75"/>
+      <c r="AP15" s="74"/>
+      <c r="AQ15" s="75"/>
+      <c r="AR15" s="74"/>
+      <c r="AS15" s="76"/>
+      <c r="AT15" s="76"/>
+      <c r="AU15" s="75"/>
     </row>
     <row r="16" spans="1:47" ht="65.5" customHeight="1">
       <c r="A16" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="36"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="57"/>
       <c r="F16" s="21">
         <v>1</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="31" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="59"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="31" t="s">
+      <c r="N16" s="59"/>
+      <c r="O16" s="59"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="31" t="s">
+      <c r="S16" s="56"/>
+      <c r="T16" s="56"/>
+      <c r="U16" s="56"/>
+      <c r="V16" s="57"/>
+      <c r="W16" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="32"/>
-      <c r="AB16" s="33"/>
+      <c r="X16" s="59"/>
+      <c r="Y16" s="59"/>
+      <c r="Z16" s="59"/>
+      <c r="AA16" s="59"/>
+      <c r="AB16" s="60"/>
       <c r="AC16" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="AD16" s="37"/>
-      <c r="AE16" s="38"/>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="37"/>
-      <c r="AH16" s="38"/>
-      <c r="AI16" s="39"/>
-      <c r="AJ16" s="37"/>
-      <c r="AK16" s="39"/>
-      <c r="AL16" s="37"/>
-      <c r="AM16" s="39"/>
-      <c r="AN16" s="37"/>
-      <c r="AO16" s="39"/>
-      <c r="AP16" s="37"/>
-      <c r="AQ16" s="39"/>
-      <c r="AR16" s="37"/>
-      <c r="AS16" s="38"/>
-      <c r="AT16" s="38"/>
-      <c r="AU16" s="39"/>
+      <c r="AD16" s="61"/>
+      <c r="AE16" s="62"/>
+      <c r="AF16" s="63"/>
+      <c r="AG16" s="61"/>
+      <c r="AH16" s="62"/>
+      <c r="AI16" s="63"/>
+      <c r="AJ16" s="61"/>
+      <c r="AK16" s="63"/>
+      <c r="AL16" s="61"/>
+      <c r="AM16" s="63"/>
+      <c r="AN16" s="61"/>
+      <c r="AO16" s="63"/>
+      <c r="AP16" s="61"/>
+      <c r="AQ16" s="63"/>
+      <c r="AR16" s="61"/>
+      <c r="AS16" s="62"/>
+      <c r="AT16" s="62"/>
+      <c r="AU16" s="63"/>
     </row>
     <row r="17" spans="1:47" ht="56" customHeight="1">
       <c r="A17" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="57"/>
       <c r="F17" s="21">
         <v>2</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="34" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="31" t="s">
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="34" t="s">
+      <c r="S17" s="56"/>
+      <c r="T17" s="56"/>
+      <c r="U17" s="56"/>
+      <c r="V17" s="57"/>
+      <c r="W17" s="78" t="s">
         <v>130</v>
       </c>
-      <c r="X17" s="41"/>
-      <c r="Y17" s="41"/>
-      <c r="Z17" s="41"/>
-      <c r="AA17" s="41"/>
-      <c r="AB17" s="41"/>
+      <c r="X17" s="79"/>
+      <c r="Y17" s="79"/>
+      <c r="Z17" s="79"/>
+      <c r="AA17" s="79"/>
+      <c r="AB17" s="79"/>
       <c r="AC17" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="AD17" s="37"/>
-      <c r="AE17" s="38"/>
-      <c r="AF17" s="39"/>
-      <c r="AG17" s="37"/>
-      <c r="AH17" s="38"/>
-      <c r="AI17" s="39"/>
-      <c r="AJ17" s="37"/>
-      <c r="AK17" s="39"/>
-      <c r="AL17" s="37"/>
-      <c r="AM17" s="39"/>
-      <c r="AN17" s="37"/>
-      <c r="AO17" s="39"/>
-      <c r="AP17" s="37"/>
-      <c r="AQ17" s="39"/>
-      <c r="AR17" s="37"/>
-      <c r="AS17" s="38"/>
-      <c r="AT17" s="38"/>
-      <c r="AU17" s="39"/>
-    </row>
-    <row r="18" spans="1:47" s="117" customFormat="1" ht="68.5" customHeight="1">
-      <c r="A18" s="107" t="s">
+      <c r="AD17" s="61"/>
+      <c r="AE17" s="62"/>
+      <c r="AF17" s="63"/>
+      <c r="AG17" s="61"/>
+      <c r="AH17" s="62"/>
+      <c r="AI17" s="63"/>
+      <c r="AJ17" s="61"/>
+      <c r="AK17" s="63"/>
+      <c r="AL17" s="61"/>
+      <c r="AM17" s="63"/>
+      <c r="AN17" s="61"/>
+      <c r="AO17" s="63"/>
+      <c r="AP17" s="61"/>
+      <c r="AQ17" s="63"/>
+      <c r="AR17" s="61"/>
+      <c r="AS17" s="62"/>
+      <c r="AT17" s="62"/>
+      <c r="AU17" s="63"/>
+    </row>
+    <row r="18" spans="1:47" s="31" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A18" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="109"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="111">
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="29">
         <v>3</v>
       </c>
-      <c r="G18" s="112" t="s">
+      <c r="G18" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="H18" s="112"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="113"/>
-      <c r="L18" s="113"/>
-      <c r="M18" s="112" t="s">
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="N18" s="112"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="114" t="s">
+      <c r="N18" s="50"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="S18" s="109"/>
-      <c r="T18" s="109"/>
-      <c r="U18" s="109"/>
-      <c r="V18" s="110"/>
-      <c r="W18" s="112" t="s">
+      <c r="S18" s="48"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="48"/>
+      <c r="V18" s="49"/>
+      <c r="W18" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="X18" s="113"/>
-      <c r="Y18" s="113"/>
-      <c r="Z18" s="113"/>
-      <c r="AA18" s="113"/>
-      <c r="AB18" s="113"/>
-      <c r="AC18" s="115"/>
-      <c r="AD18" s="116"/>
-      <c r="AE18" s="116"/>
-      <c r="AF18" s="116"/>
-      <c r="AG18" s="116"/>
-      <c r="AH18" s="116"/>
-      <c r="AI18" s="116"/>
-      <c r="AJ18" s="116"/>
-      <c r="AK18" s="116"/>
-      <c r="AL18" s="116"/>
-      <c r="AM18" s="116"/>
-      <c r="AN18" s="116"/>
-      <c r="AO18" s="116"/>
-      <c r="AP18" s="116"/>
-      <c r="AQ18" s="116"/>
-      <c r="AR18" s="116"/>
-      <c r="AS18" s="116"/>
-      <c r="AT18" s="116"/>
-      <c r="AU18" s="116"/>
-    </row>
-    <row r="19" spans="1:47" s="117" customFormat="1" ht="68.5" customHeight="1">
-      <c r="A19" s="107" t="s">
+      <c r="X18" s="51"/>
+      <c r="Y18" s="51"/>
+      <c r="Z18" s="51"/>
+      <c r="AA18" s="51"/>
+      <c r="AB18" s="51"/>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="46"/>
+      <c r="AE18" s="46"/>
+      <c r="AF18" s="46"/>
+      <c r="AG18" s="46"/>
+      <c r="AH18" s="46"/>
+      <c r="AI18" s="46"/>
+      <c r="AJ18" s="46"/>
+      <c r="AK18" s="46"/>
+      <c r="AL18" s="46"/>
+      <c r="AM18" s="46"/>
+      <c r="AN18" s="46"/>
+      <c r="AO18" s="46"/>
+      <c r="AP18" s="46"/>
+      <c r="AQ18" s="46"/>
+      <c r="AR18" s="46"/>
+      <c r="AS18" s="46"/>
+      <c r="AT18" s="46"/>
+      <c r="AU18" s="46"/>
+    </row>
+    <row r="19" spans="1:47" s="31" customFormat="1" ht="68.5" customHeight="1">
+      <c r="A19" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="109"/>
-      <c r="D19" s="109"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="111">
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="29">
         <v>4</v>
       </c>
-      <c r="G19" s="112" t="s">
+      <c r="G19" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="113"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="112" t="s">
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="114" t="s">
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="S19" s="109"/>
-      <c r="T19" s="109"/>
-      <c r="U19" s="109"/>
-      <c r="V19" s="110"/>
-      <c r="W19" s="112" t="s">
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="X19" s="113"/>
-      <c r="Y19" s="113"/>
-      <c r="Z19" s="113"/>
-      <c r="AA19" s="113"/>
-      <c r="AB19" s="113"/>
-      <c r="AC19" s="115"/>
-      <c r="AD19" s="116"/>
-      <c r="AE19" s="116"/>
-      <c r="AF19" s="116"/>
-      <c r="AG19" s="116"/>
-      <c r="AH19" s="116"/>
-      <c r="AI19" s="116"/>
-      <c r="AJ19" s="116"/>
-      <c r="AK19" s="116"/>
-      <c r="AL19" s="116"/>
-      <c r="AM19" s="116"/>
-      <c r="AN19" s="116"/>
-      <c r="AO19" s="116"/>
-      <c r="AP19" s="116"/>
-      <c r="AQ19" s="116"/>
-      <c r="AR19" s="116"/>
-      <c r="AS19" s="116"/>
-      <c r="AT19" s="116"/>
-      <c r="AU19" s="116"/>
-    </row>
-    <row r="20" spans="1:47" s="142" customFormat="1" ht="70" customHeight="1">
-      <c r="A20" s="134" t="s">
+      <c r="X19" s="51"/>
+      <c r="Y19" s="51"/>
+      <c r="Z19" s="51"/>
+      <c r="AA19" s="51"/>
+      <c r="AB19" s="51"/>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="46"/>
+      <c r="AE19" s="46"/>
+      <c r="AF19" s="46"/>
+      <c r="AG19" s="46"/>
+      <c r="AH19" s="46"/>
+      <c r="AI19" s="46"/>
+      <c r="AJ19" s="46"/>
+      <c r="AK19" s="46"/>
+      <c r="AL19" s="46"/>
+      <c r="AM19" s="46"/>
+      <c r="AN19" s="46"/>
+      <c r="AO19" s="46"/>
+      <c r="AP19" s="46"/>
+      <c r="AQ19" s="46"/>
+      <c r="AR19" s="46"/>
+      <c r="AS19" s="46"/>
+      <c r="AT19" s="46"/>
+      <c r="AU19" s="46"/>
+    </row>
+    <row r="20" spans="1:47" s="39" customFormat="1" ht="70" customHeight="1">
+      <c r="A20" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="135" t="s">
+      <c r="B20" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="136"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="138">
+      <c r="C20" s="66"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="37">
         <v>5</v>
       </c>
-      <c r="G20" s="135" t="s">
+      <c r="G20" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H20" s="136"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="136"/>
-      <c r="K20" s="136"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="139" t="s">
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="N20" s="139"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="139"/>
-      <c r="Q20" s="139"/>
-      <c r="R20" s="135" t="s">
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="64"/>
+      <c r="R20" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="S20" s="136"/>
-      <c r="T20" s="136"/>
-      <c r="U20" s="136"/>
-      <c r="V20" s="137"/>
-      <c r="W20" s="139" t="s">
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="X20" s="139"/>
-      <c r="Y20" s="139"/>
-      <c r="Z20" s="139"/>
-      <c r="AA20" s="139"/>
-      <c r="AB20" s="139"/>
-      <c r="AC20" s="140" t="s">
+      <c r="X20" s="64"/>
+      <c r="Y20" s="64"/>
+      <c r="Z20" s="64"/>
+      <c r="AA20" s="64"/>
+      <c r="AB20" s="64"/>
+      <c r="AC20" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="AD20" s="141"/>
-      <c r="AE20" s="141"/>
-      <c r="AF20" s="141"/>
-      <c r="AG20" s="141"/>
-      <c r="AH20" s="141"/>
-      <c r="AI20" s="141"/>
-      <c r="AJ20" s="141"/>
-      <c r="AK20" s="141"/>
-      <c r="AL20" s="141"/>
-      <c r="AM20" s="141"/>
-      <c r="AN20" s="141"/>
-      <c r="AO20" s="141"/>
-      <c r="AP20" s="141"/>
-      <c r="AQ20" s="141"/>
-      <c r="AR20" s="141"/>
-      <c r="AS20" s="141"/>
-      <c r="AT20" s="141"/>
-      <c r="AU20" s="141"/>
-    </row>
-    <row r="21" spans="1:47" s="142" customFormat="1" ht="72" customHeight="1">
-      <c r="A21" s="134" t="s">
+      <c r="AD20" s="54"/>
+      <c r="AE20" s="54"/>
+      <c r="AF20" s="54"/>
+      <c r="AG20" s="54"/>
+      <c r="AH20" s="54"/>
+      <c r="AI20" s="54"/>
+      <c r="AJ20" s="54"/>
+      <c r="AK20" s="54"/>
+      <c r="AL20" s="54"/>
+      <c r="AM20" s="54"/>
+      <c r="AN20" s="54"/>
+      <c r="AO20" s="54"/>
+      <c r="AP20" s="54"/>
+      <c r="AQ20" s="54"/>
+      <c r="AR20" s="54"/>
+      <c r="AS20" s="54"/>
+      <c r="AT20" s="54"/>
+      <c r="AU20" s="54"/>
+    </row>
+    <row r="21" spans="1:47" s="39" customFormat="1" ht="72" customHeight="1">
+      <c r="A21" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="135" t="s">
+      <c r="B21" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="136"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="138">
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="37">
         <v>6</v>
       </c>
-      <c r="G21" s="135" t="s">
+      <c r="G21" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="H21" s="136"/>
-      <c r="I21" s="136"/>
-      <c r="J21" s="136"/>
-      <c r="K21" s="136"/>
-      <c r="L21" s="137"/>
-      <c r="M21" s="135" t="s">
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="N21" s="136"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="136"/>
-      <c r="Q21" s="137"/>
-      <c r="R21" s="135" t="s">
+      <c r="N21" s="66"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="66"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="S21" s="136"/>
-      <c r="T21" s="136"/>
-      <c r="U21" s="136"/>
-      <c r="V21" s="137"/>
-      <c r="W21" s="139" t="s">
+      <c r="S21" s="66"/>
+      <c r="T21" s="66"/>
+      <c r="U21" s="66"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="X21" s="139"/>
-      <c r="Y21" s="139"/>
-      <c r="Z21" s="139"/>
-      <c r="AA21" s="139"/>
-      <c r="AB21" s="139"/>
-      <c r="AC21" s="140" t="s">
+      <c r="X21" s="64"/>
+      <c r="Y21" s="64"/>
+      <c r="Z21" s="64"/>
+      <c r="AA21" s="64"/>
+      <c r="AB21" s="64"/>
+      <c r="AC21" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="AD21" s="141"/>
-      <c r="AE21" s="141"/>
-      <c r="AF21" s="141"/>
-      <c r="AG21" s="141"/>
-      <c r="AH21" s="141"/>
-      <c r="AI21" s="141"/>
-      <c r="AJ21" s="141"/>
-      <c r="AK21" s="141"/>
-      <c r="AL21" s="141"/>
-      <c r="AM21" s="141"/>
-      <c r="AN21" s="141"/>
-      <c r="AO21" s="141"/>
-      <c r="AP21" s="141"/>
-      <c r="AQ21" s="141"/>
-      <c r="AR21" s="141"/>
-      <c r="AS21" s="141"/>
-      <c r="AT21" s="141"/>
-      <c r="AU21" s="141"/>
-    </row>
-    <row r="22" spans="1:47" s="146" customFormat="1" ht="72" customHeight="1">
-      <c r="A22" s="134" t="s">
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="54"/>
+      <c r="AF21" s="54"/>
+      <c r="AG21" s="54"/>
+      <c r="AH21" s="54"/>
+      <c r="AI21" s="54"/>
+      <c r="AJ21" s="54"/>
+      <c r="AK21" s="54"/>
+      <c r="AL21" s="54"/>
+      <c r="AM21" s="54"/>
+      <c r="AN21" s="54"/>
+      <c r="AO21" s="54"/>
+      <c r="AP21" s="54"/>
+      <c r="AQ21" s="54"/>
+      <c r="AR21" s="54"/>
+      <c r="AS21" s="54"/>
+      <c r="AT21" s="54"/>
+      <c r="AU21" s="54"/>
+    </row>
+    <row r="22" spans="1:47" s="41" customFormat="1" ht="72" customHeight="1">
+      <c r="A22" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="134" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="138">
+      <c r="C22" s="135"/>
+      <c r="D22" s="135"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="37">
         <v>1</v>
       </c>
-      <c r="G22" s="139" t="s">
+      <c r="G22" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="H22" s="139"/>
-      <c r="I22" s="139"/>
-      <c r="J22" s="139"/>
-      <c r="K22" s="139"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="143" t="s">
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="137" t="s">
         <v>79</v>
       </c>
-      <c r="N22" s="136"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="136"/>
-      <c r="Q22" s="136"/>
-      <c r="R22" s="135" t="s">
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="65" t="s">
         <v>141</v>
       </c>
-      <c r="S22" s="136"/>
-      <c r="T22" s="136"/>
-      <c r="U22" s="136"/>
-      <c r="V22" s="137"/>
-      <c r="W22" s="139" t="s">
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="X22" s="139"/>
-      <c r="Y22" s="139"/>
-      <c r="Z22" s="139"/>
-      <c r="AA22" s="139"/>
-      <c r="AB22" s="139"/>
-      <c r="AC22" s="144" t="s">
+      <c r="X22" s="64"/>
+      <c r="Y22" s="64"/>
+      <c r="Z22" s="64"/>
+      <c r="AA22" s="64"/>
+      <c r="AB22" s="64"/>
+      <c r="AC22" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="AD22" s="145"/>
-      <c r="AE22" s="145"/>
-      <c r="AF22" s="145"/>
-      <c r="AG22" s="145"/>
-      <c r="AH22" s="145"/>
-      <c r="AI22" s="145"/>
-      <c r="AJ22" s="145"/>
-      <c r="AK22" s="145"/>
-      <c r="AL22" s="145"/>
-      <c r="AM22" s="145"/>
-      <c r="AN22" s="145"/>
-      <c r="AO22" s="145"/>
-      <c r="AP22" s="145"/>
-      <c r="AQ22" s="145"/>
-      <c r="AR22" s="145"/>
-      <c r="AS22" s="145"/>
-      <c r="AT22" s="145"/>
-      <c r="AU22" s="145"/>
-    </row>
-    <row r="23" spans="1:47" s="159" customFormat="1" ht="72" customHeight="1">
-      <c r="A23" s="147" t="s">
+      <c r="AD22" s="68"/>
+      <c r="AE22" s="68"/>
+      <c r="AF22" s="68"/>
+      <c r="AG22" s="68"/>
+      <c r="AH22" s="68"/>
+      <c r="AI22" s="68"/>
+      <c r="AJ22" s="68"/>
+      <c r="AK22" s="68"/>
+      <c r="AL22" s="68"/>
+      <c r="AM22" s="68"/>
+      <c r="AN22" s="68"/>
+      <c r="AO22" s="68"/>
+      <c r="AP22" s="68"/>
+      <c r="AQ22" s="68"/>
+      <c r="AR22" s="68"/>
+      <c r="AS22" s="68"/>
+      <c r="AT22" s="68"/>
+      <c r="AU22" s="68"/>
+    </row>
+    <row r="23" spans="1:47" s="45" customFormat="1" ht="72" customHeight="1">
+      <c r="A23" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="148" t="s">
+      <c r="B23" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="149"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="151">
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="43">
         <v>2</v>
       </c>
-      <c r="G23" s="152" t="s">
+      <c r="G23" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="H23" s="152"/>
-      <c r="I23" s="152"/>
-      <c r="J23" s="152"/>
-      <c r="K23" s="152"/>
-      <c r="L23" s="152"/>
-      <c r="M23" s="153" t="s">
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="N23" s="154"/>
-      <c r="O23" s="154"/>
-      <c r="P23" s="154"/>
-      <c r="Q23" s="154"/>
-      <c r="R23" s="155" t="s">
+      <c r="N23" s="82"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="96" t="s">
         <v>142</v>
       </c>
-      <c r="S23" s="154"/>
-      <c r="T23" s="154"/>
-      <c r="U23" s="154"/>
-      <c r="V23" s="156"/>
-      <c r="W23" s="152" t="s">
+      <c r="S23" s="82"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="82"/>
+      <c r="V23" s="97"/>
+      <c r="W23" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="X23" s="152"/>
-      <c r="Y23" s="152"/>
-      <c r="Z23" s="152"/>
-      <c r="AA23" s="152"/>
-      <c r="AB23" s="152"/>
-      <c r="AC23" s="157" t="s">
+      <c r="X23" s="53"/>
+      <c r="Y23" s="53"/>
+      <c r="Z23" s="53"/>
+      <c r="AA23" s="53"/>
+      <c r="AB23" s="53"/>
+      <c r="AC23" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="AD23" s="158"/>
-      <c r="AE23" s="158"/>
-      <c r="AF23" s="158"/>
-      <c r="AG23" s="158"/>
-      <c r="AH23" s="158"/>
-      <c r="AI23" s="158"/>
-      <c r="AJ23" s="158"/>
-      <c r="AK23" s="158"/>
-      <c r="AL23" s="158"/>
-      <c r="AM23" s="158"/>
-      <c r="AN23" s="158"/>
-      <c r="AO23" s="158"/>
-      <c r="AP23" s="158"/>
-      <c r="AQ23" s="158"/>
-      <c r="AR23" s="158"/>
-      <c r="AS23" s="158"/>
-      <c r="AT23" s="158"/>
-      <c r="AU23" s="158"/>
+      <c r="AD23" s="80"/>
+      <c r="AE23" s="80"/>
+      <c r="AF23" s="80"/>
+      <c r="AG23" s="80"/>
+      <c r="AH23" s="80"/>
+      <c r="AI23" s="80"/>
+      <c r="AJ23" s="80"/>
+      <c r="AK23" s="80"/>
+      <c r="AL23" s="80"/>
+      <c r="AM23" s="80"/>
+      <c r="AN23" s="80"/>
+      <c r="AO23" s="80"/>
+      <c r="AP23" s="80"/>
+      <c r="AQ23" s="80"/>
+      <c r="AR23" s="80"/>
+      <c r="AS23" s="80"/>
+      <c r="AT23" s="80"/>
+      <c r="AU23" s="80"/>
     </row>
     <row r="24" spans="1:47" ht="68.5" customHeight="1">
       <c r="A24" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="36"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="57"/>
       <c r="F24" s="21">
         <v>3</v>
       </c>
-      <c r="G24" s="34" t="s">
+      <c r="G24" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="34" t="s">
+      <c r="H24" s="78"/>
+      <c r="I24" s="78"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34" t="s">
+      <c r="N24" s="78"/>
+      <c r="O24" s="78"/>
+      <c r="P24" s="78"/>
+      <c r="Q24" s="78"/>
+      <c r="R24" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="S24" s="41"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="34" t="s">
+      <c r="S24" s="79"/>
+      <c r="T24" s="79"/>
+      <c r="U24" s="79"/>
+      <c r="V24" s="79"/>
+      <c r="W24" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="X24" s="41"/>
-      <c r="Y24" s="41"/>
-      <c r="Z24" s="41"/>
-      <c r="AA24" s="41"/>
-      <c r="AB24" s="41"/>
+      <c r="X24" s="79"/>
+      <c r="Y24" s="79"/>
+      <c r="Z24" s="79"/>
+      <c r="AA24" s="79"/>
+      <c r="AB24" s="79"/>
       <c r="AC24" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="AD24" s="40"/>
-      <c r="AE24" s="40"/>
-      <c r="AF24" s="40"/>
-      <c r="AG24" s="40"/>
-      <c r="AH24" s="40"/>
-      <c r="AI24" s="40"/>
-      <c r="AJ24" s="40"/>
-      <c r="AK24" s="40"/>
-      <c r="AL24" s="40"/>
-      <c r="AM24" s="40"/>
-      <c r="AN24" s="40"/>
-      <c r="AO24" s="40"/>
-      <c r="AP24" s="40"/>
-      <c r="AQ24" s="40"/>
-      <c r="AR24" s="40"/>
-      <c r="AS24" s="40"/>
-      <c r="AT24" s="40"/>
-      <c r="AU24" s="40"/>
+      <c r="AD24" s="70"/>
+      <c r="AE24" s="70"/>
+      <c r="AF24" s="70"/>
+      <c r="AG24" s="70"/>
+      <c r="AH24" s="70"/>
+      <c r="AI24" s="70"/>
+      <c r="AJ24" s="70"/>
+      <c r="AK24" s="70"/>
+      <c r="AL24" s="70"/>
+      <c r="AM24" s="70"/>
+      <c r="AN24" s="70"/>
+      <c r="AO24" s="70"/>
+      <c r="AP24" s="70"/>
+      <c r="AQ24" s="70"/>
+      <c r="AR24" s="70"/>
+      <c r="AS24" s="70"/>
+      <c r="AT24" s="70"/>
+      <c r="AU24" s="70"/>
     </row>
     <row r="25" spans="1:47" ht="68.5" customHeight="1">
       <c r="A25" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="36"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="57"/>
       <c r="F25" s="21">
         <v>4</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G25" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="34" t="s">
+      <c r="H25" s="78"/>
+      <c r="I25" s="78"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="79"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34" t="s">
+      <c r="N25" s="78"/>
+      <c r="O25" s="78"/>
+      <c r="P25" s="78"/>
+      <c r="Q25" s="78"/>
+      <c r="R25" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="S25" s="41"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="41"/>
-      <c r="W25" s="34" t="s">
+      <c r="S25" s="79"/>
+      <c r="T25" s="79"/>
+      <c r="U25" s="79"/>
+      <c r="V25" s="79"/>
+      <c r="W25" s="78" t="s">
         <v>129</v>
       </c>
-      <c r="X25" s="41"/>
-      <c r="Y25" s="41"/>
-      <c r="Z25" s="41"/>
-      <c r="AA25" s="41"/>
-      <c r="AB25" s="41"/>
+      <c r="X25" s="79"/>
+      <c r="Y25" s="79"/>
+      <c r="Z25" s="79"/>
+      <c r="AA25" s="79"/>
+      <c r="AB25" s="79"/>
       <c r="AC25" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="AD25" s="40"/>
-      <c r="AE25" s="40"/>
-      <c r="AF25" s="40"/>
-      <c r="AG25" s="40"/>
-      <c r="AH25" s="40"/>
-      <c r="AI25" s="40"/>
-      <c r="AJ25" s="40"/>
-      <c r="AK25" s="40"/>
-      <c r="AL25" s="40"/>
-      <c r="AM25" s="40"/>
-      <c r="AN25" s="40"/>
-      <c r="AO25" s="40"/>
-      <c r="AP25" s="40"/>
-      <c r="AQ25" s="40"/>
-      <c r="AR25" s="40"/>
-      <c r="AS25" s="40"/>
-      <c r="AT25" s="40"/>
-      <c r="AU25" s="40"/>
+      <c r="AD25" s="70"/>
+      <c r="AE25" s="70"/>
+      <c r="AF25" s="70"/>
+      <c r="AG25" s="70"/>
+      <c r="AH25" s="70"/>
+      <c r="AI25" s="70"/>
+      <c r="AJ25" s="70"/>
+      <c r="AK25" s="70"/>
+      <c r="AL25" s="70"/>
+      <c r="AM25" s="70"/>
+      <c r="AN25" s="70"/>
+      <c r="AO25" s="70"/>
+      <c r="AP25" s="70"/>
+      <c r="AQ25" s="70"/>
+      <c r="AR25" s="70"/>
+      <c r="AS25" s="70"/>
+      <c r="AT25" s="70"/>
+      <c r="AU25" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="224">
-    <mergeCell ref="AP18:AQ18"/>
-    <mergeCell ref="AR18:AU18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="R19:V19"/>
-    <mergeCell ref="W19:AB19"/>
-    <mergeCell ref="AD19:AF19"/>
-    <mergeCell ref="AG19:AI19"/>
-    <mergeCell ref="AJ19:AK19"/>
-    <mergeCell ref="AL19:AM19"/>
-    <mergeCell ref="AN19:AO19"/>
-    <mergeCell ref="AP19:AQ19"/>
-    <mergeCell ref="AR19:AU19"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="AD20:AF20"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="R16:V16"/>
-    <mergeCell ref="W16:AB16"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="AG16:AI16"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AG18:AI18"/>
+    <mergeCell ref="AJ22:AK22"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="G15:L15"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="R15:V15"/>
+    <mergeCell ref="W15:AB15"/>
+    <mergeCell ref="AD15:AF15"/>
+    <mergeCell ref="AG15:AI15"/>
+    <mergeCell ref="AJ15:AK15"/>
+    <mergeCell ref="AL15:AM15"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="W17:AB17"/>
+    <mergeCell ref="AD17:AF17"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="AJ17:AK17"/>
+    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="AR20:AU20"/>
+    <mergeCell ref="AP14:AQ14"/>
+    <mergeCell ref="AP11:AQ11"/>
+    <mergeCell ref="AN22:AO22"/>
+    <mergeCell ref="AP22:AQ22"/>
+    <mergeCell ref="AR22:AU22"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="G25:L25"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="R25:V25"/>
+    <mergeCell ref="W25:AB25"/>
+    <mergeCell ref="AD25:AF25"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AK25"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="AN25:AO25"/>
+    <mergeCell ref="AP25:AQ25"/>
+    <mergeCell ref="AR25:AU25"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="R22:V22"/>
+    <mergeCell ref="W22:AB22"/>
+    <mergeCell ref="AD22:AF22"/>
+    <mergeCell ref="AN21:AO21"/>
+    <mergeCell ref="AP21:AQ21"/>
+    <mergeCell ref="AR21:AU21"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="W21:AB21"/>
+    <mergeCell ref="AD21:AF21"/>
+    <mergeCell ref="AG21:AI21"/>
+    <mergeCell ref="AJ21:AK21"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="G17:L17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="AP20:AQ20"/>
+    <mergeCell ref="AP13:AQ13"/>
+    <mergeCell ref="W10:AB10"/>
+    <mergeCell ref="W11:AB11"/>
+    <mergeCell ref="W12:AB12"/>
+    <mergeCell ref="AJ20:AK20"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AG20:AI20"/>
+    <mergeCell ref="AD11:AF11"/>
+    <mergeCell ref="AD12:AF12"/>
+    <mergeCell ref="AD13:AF13"/>
+    <mergeCell ref="AJ10:AK10"/>
+    <mergeCell ref="AJ11:AK11"/>
+    <mergeCell ref="AJ12:AK12"/>
+    <mergeCell ref="AJ13:AK13"/>
+    <mergeCell ref="AJ14:AK14"/>
+    <mergeCell ref="W13:AB13"/>
+    <mergeCell ref="W14:AB14"/>
+    <mergeCell ref="W20:AB20"/>
+    <mergeCell ref="AN14:AO14"/>
+    <mergeCell ref="AN20:AO20"/>
+    <mergeCell ref="AL10:AM10"/>
+    <mergeCell ref="AL11:AM11"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AN15:AO15"/>
+    <mergeCell ref="AN17:AO17"/>
+    <mergeCell ref="AL17:AM17"/>
+    <mergeCell ref="AL18:AM18"/>
+    <mergeCell ref="AN18:AO18"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="D8:M8"/>
+    <mergeCell ref="AP10:AQ10"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="R23:V23"/>
+    <mergeCell ref="W23:AB23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="AP17:AQ17"/>
+    <mergeCell ref="AR17:AU17"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="R18:V18"/>
+    <mergeCell ref="W18:AB18"/>
+    <mergeCell ref="AD18:AF18"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G24:L24"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="R24:V24"/>
+    <mergeCell ref="W24:AB24"/>
+    <mergeCell ref="AD24:AF24"/>
+    <mergeCell ref="AN23:AO23"/>
+    <mergeCell ref="AP23:AQ23"/>
+    <mergeCell ref="AR23:AU23"/>
+    <mergeCell ref="AJ23:AK23"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AG24:AI24"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="AN24:AO24"/>
+    <mergeCell ref="AP24:AQ24"/>
+    <mergeCell ref="AR24:AU24"/>
+    <mergeCell ref="AJ24:AK24"/>
+    <mergeCell ref="G10:L10"/>
     <mergeCell ref="R12:V12"/>
     <mergeCell ref="R13:V13"/>
     <mergeCell ref="R14:V14"/>
@@ -3488,177 +3630,35 @@
     <mergeCell ref="AN11:AO11"/>
     <mergeCell ref="AN12:AO12"/>
     <mergeCell ref="AN13:AO13"/>
-    <mergeCell ref="AP17:AQ17"/>
-    <mergeCell ref="AR17:AU17"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="R18:V18"/>
-    <mergeCell ref="W18:AB18"/>
-    <mergeCell ref="AD18:AF18"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="R24:V24"/>
-    <mergeCell ref="W24:AB24"/>
-    <mergeCell ref="AD24:AF24"/>
-    <mergeCell ref="AN23:AO23"/>
-    <mergeCell ref="AP23:AQ23"/>
-    <mergeCell ref="AR23:AU23"/>
-    <mergeCell ref="AJ23:AK23"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="AN24:AO24"/>
-    <mergeCell ref="AP24:AQ24"/>
-    <mergeCell ref="AR24:AU24"/>
-    <mergeCell ref="AJ24:AK24"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D7:M7"/>
-    <mergeCell ref="D8:M8"/>
-    <mergeCell ref="AP10:AQ10"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="R23:V23"/>
-    <mergeCell ref="W23:AB23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AG23:AI23"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="R20:V20"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="AN14:AO14"/>
-    <mergeCell ref="AN20:AO20"/>
-    <mergeCell ref="AL10:AM10"/>
-    <mergeCell ref="AL11:AM11"/>
-    <mergeCell ref="AL12:AM12"/>
-    <mergeCell ref="AN15:AO15"/>
-    <mergeCell ref="AN17:AO17"/>
-    <mergeCell ref="AL17:AM17"/>
-    <mergeCell ref="AL18:AM18"/>
-    <mergeCell ref="AN18:AO18"/>
-    <mergeCell ref="AP20:AQ20"/>
-    <mergeCell ref="AP13:AQ13"/>
-    <mergeCell ref="W10:AB10"/>
-    <mergeCell ref="W11:AB11"/>
-    <mergeCell ref="W12:AB12"/>
-    <mergeCell ref="AJ20:AK20"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AG12:AI12"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="AG14:AI14"/>
-    <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="AD11:AF11"/>
-    <mergeCell ref="AD12:AF12"/>
-    <mergeCell ref="AD13:AF13"/>
-    <mergeCell ref="AJ10:AK10"/>
-    <mergeCell ref="AJ11:AK11"/>
-    <mergeCell ref="AJ12:AK12"/>
-    <mergeCell ref="AJ13:AK13"/>
-    <mergeCell ref="AJ14:AK14"/>
-    <mergeCell ref="W13:AB13"/>
-    <mergeCell ref="W14:AB14"/>
-    <mergeCell ref="W20:AB20"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="M11:Q11"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="M13:Q13"/>
-    <mergeCell ref="M14:Q14"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="AN21:AO21"/>
-    <mergeCell ref="AP21:AQ21"/>
-    <mergeCell ref="AR21:AU21"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="R21:V21"/>
-    <mergeCell ref="W21:AB21"/>
-    <mergeCell ref="AD21:AF21"/>
-    <mergeCell ref="AG21:AI21"/>
-    <mergeCell ref="AJ21:AK21"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AR20:AU20"/>
-    <mergeCell ref="AP14:AQ14"/>
-    <mergeCell ref="AP11:AQ11"/>
-    <mergeCell ref="AN22:AO22"/>
-    <mergeCell ref="AP22:AQ22"/>
-    <mergeCell ref="AR22:AU22"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="G25:L25"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="R25:V25"/>
-    <mergeCell ref="W25:AB25"/>
-    <mergeCell ref="AD25:AF25"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AK25"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="AN25:AO25"/>
-    <mergeCell ref="AP25:AQ25"/>
-    <mergeCell ref="AR25:AU25"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="R22:V22"/>
-    <mergeCell ref="W22:AB22"/>
-    <mergeCell ref="AD22:AF22"/>
-    <mergeCell ref="AJ22:AK22"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="G15:L15"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="R15:V15"/>
-    <mergeCell ref="W15:AB15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="AG15:AI15"/>
-    <mergeCell ref="AJ15:AK15"/>
-    <mergeCell ref="AL15:AM15"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="W17:AB17"/>
-    <mergeCell ref="AD17:AF17"/>
-    <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="AJ17:AK17"/>
-    <mergeCell ref="AJ18:AK18"/>
+    <mergeCell ref="G23:L23"/>
+    <mergeCell ref="AD20:AF20"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="G16:L16"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="R16:V16"/>
+    <mergeCell ref="W16:AB16"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="AG22:AI22"/>
+    <mergeCell ref="AG18:AI18"/>
+    <mergeCell ref="AP18:AQ18"/>
+    <mergeCell ref="AR18:AU18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="R19:V19"/>
+    <mergeCell ref="W19:AB19"/>
+    <mergeCell ref="AD19:AF19"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="AJ19:AK19"/>
+    <mergeCell ref="AL19:AM19"/>
+    <mergeCell ref="AN19:AO19"/>
+    <mergeCell ref="AP19:AQ19"/>
+    <mergeCell ref="AR19:AU19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3679,42 +3679,42 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="97"/>
+      <c r="B2" s="150"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="97"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="94" t="s">
+      <c r="A3" s="150"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="147" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="95"/>
-      <c r="E3" s="94" t="s">
+      <c r="D3" s="148"/>
+      <c r="E3" s="147" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="95"/>
+      <c r="F3" s="148"/>
     </row>
     <row r="4" spans="1:6" ht="37" customHeight="1">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="96" t="s">
+      <c r="C4" s="149" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96" t="s">
+      <c r="D4" s="149"/>
+      <c r="E4" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="96"/>
+      <c r="F4" s="149"/>
     </row>
     <row r="5" spans="1:6" ht="37" customHeight="1">
-      <c r="A5" s="101"/>
-      <c r="B5" s="103"/>
+      <c r="A5" s="154"/>
+      <c r="B5" s="156"/>
       <c r="C5" s="5" t="s">
         <v>45</v>
       </c>
@@ -4209,60 +4209,60 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="106" t="s">
+      <c r="A31" s="159" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="106"/>
-      <c r="C31" s="106"/>
+      <c r="B31" s="159"/>
+      <c r="C31" s="159"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="98" t="s">
+      <c r="B32" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="99"/>
+      <c r="C32" s="152"/>
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="98" t="s">
+      <c r="B33" s="151" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="99"/>
+      <c r="C33" s="152"/>
       <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="104" t="s">
+      <c r="B34" s="157" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="105"/>
+      <c r="C34" s="158"/>
       <c r="D34" s="9"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="98" t="s">
+      <c r="B35" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="99"/>
+      <c r="C35" s="152"/>
       <c r="D35" s="8"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="98" t="s">
+      <c r="B36" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="99"/>
+      <c r="C36" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="13">
